--- a/BVSimulationFiles/95.xlsx
+++ b/BVSimulationFiles/95.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0003902439024390245</v>
+        <v>0.000780487804878049</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003952229822256001</v>
+        <v>0.0007904459644512002</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0003989484485349945</v>
+        <v>0.000797896897069989</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004015237380270023</v>
+        <v>0.0008030474760540046</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004030454850444418</v>
+        <v>0.0008060909700888835</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004036039257997247</v>
+        <v>0.0008072078515994494</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0004032832798939254</v>
+        <v>0.0008065665597878508</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0004021621103929191</v>
+        <v>0.0008043242207858382</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004003136636207223</v>
+        <v>0.0008006273272414446</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0003978061897690383</v>
+        <v>0.0007956123795380767</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003947032453640622</v>
+        <v>0.0007894064907281244</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000391063978576623</v>
+        <v>0.000782127957153246</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0003869433983096281</v>
+        <v>0.0007738867966192562</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0003823926279473493</v>
+        <v>0.0007647852558946986</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0003774591446042299</v>
+        <v>0.0007549182892084598</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0003721870046664669</v>
+        <v>0.0007443740093329339</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003666170563774928</v>
+        <v>0.0007332341127549856</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003607871401785558</v>
+        <v>0.0007215742803571115</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0003547322774777359</v>
+        <v>0.0007094645549554718</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0003484848484848484</v>
+        <v>0.0006969696969696968</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0003902439024390245</v>
+        <v>0.000780487804878049</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0003952229822256001</v>
+        <v>0.0007904459644512002</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0003989484485349945</v>
+        <v>0.000797896897069989</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004015237380270023</v>
+        <v>0.0008030474760540046</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004030454850444418</v>
+        <v>0.0008060909700888835</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004036039257997247</v>
+        <v>0.0008072078515994494</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004032832798939254</v>
+        <v>0.0008065665597878508</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004021621103929191</v>
+        <v>0.0008043242207858382</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004003136636207223</v>
+        <v>0.0008006273272414446</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0003978061897690383</v>
+        <v>0.0007956123795380767</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003947032453640622</v>
+        <v>0.0007894064907281244</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000391063978576623</v>
+        <v>0.000782127957153246</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0003869433983096281</v>
+        <v>0.0007738867966192562</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0003823926279473493</v>
+        <v>0.0007647852558946986</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003774591446042299</v>
+        <v>0.0007549182892084598</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0003721870046664669</v>
+        <v>0.0007443740093329339</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003666170563774928</v>
+        <v>0.0007332341127549856</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003607871401785558</v>
+        <v>0.0007215742803571115</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0003547322774777359</v>
+        <v>0.0007094645549554718</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0003484848484848484</v>
+        <v>0.0006969696969696968</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/95.xlsx
+++ b/BVSimulationFiles/95.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.000780487804878049</v>
+        <v>0.00780487804878049</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007904459644512002</v>
+        <v>0.007904459644512002</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000797896897069989</v>
+        <v>0.00797896897069989</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008030474760540046</v>
+        <v>0.008030474760540045</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008060909700888835</v>
+        <v>0.008060909700888835</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008072078515994494</v>
+        <v>0.008072078515994494</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008065665597878508</v>
+        <v>0.008065665597878508</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008043242207858382</v>
+        <v>0.008043242207858382</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008006273272414446</v>
+        <v>0.008006273272414446</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007956123795380767</v>
+        <v>0.007956123795380767</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007894064907281244</v>
+        <v>0.007894064907281244</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000782127957153246</v>
+        <v>0.007821279571532459</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007738867966192562</v>
+        <v>0.007738867966192563</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0007647852558946986</v>
+        <v>0.007647852558946986</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007549182892084598</v>
+        <v>0.007549182892084599</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007443740093329339</v>
+        <v>0.007443740093329338</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007332341127549856</v>
+        <v>0.007332341127549856</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007215742803571115</v>
+        <v>0.007215742803571116</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007094645549554718</v>
+        <v>0.007094645549554718</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0006969696969696968</v>
+        <v>0.006969696969696968</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.000780487804878049</v>
+        <v>0.00780487804878049</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007904459644512002</v>
+        <v>0.007904459644512002</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000797896897069989</v>
+        <v>0.00797896897069989</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008030474760540046</v>
+        <v>0.008030474760540045</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008060909700888835</v>
+        <v>0.008060909700888835</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008072078515994494</v>
+        <v>0.008072078515994494</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008065665597878508</v>
+        <v>0.008065665597878508</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008043242207858382</v>
+        <v>0.008043242207858382</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008006273272414446</v>
+        <v>0.008006273272414446</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007956123795380767</v>
+        <v>0.007956123795380767</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007894064907281244</v>
+        <v>0.007894064907281244</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000782127957153246</v>
+        <v>0.007821279571532459</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0007738867966192562</v>
+        <v>0.007738867966192563</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0007647852558946986</v>
+        <v>0.007647852558946986</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007549182892084598</v>
+        <v>0.007549182892084599</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007443740093329339</v>
+        <v>0.007443740093329338</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007332341127549856</v>
+        <v>0.007332341127549856</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007215742803571115</v>
+        <v>0.007215742803571116</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007094645549554718</v>
+        <v>0.007094645549554718</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0006969696969696968</v>
+        <v>0.006969696969696968</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/95.xlsx
+++ b/BVSimulationFiles/95.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,61 +421,31 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.03147</v>
+        <v>0.02061827586206896</v>
       </c>
       <c r="D1" t="n">
-        <v>0.06294</v>
+        <v>0.04123655172413793</v>
       </c>
       <c r="E1" t="n">
-        <v>0.09440999999999999</v>
+        <v>0.06185482758620689</v>
       </c>
       <c r="F1" t="n">
-        <v>0.12588</v>
+        <v>0.08247310344827585</v>
       </c>
       <c r="G1" t="n">
-        <v>0.15735</v>
+        <v>0.1030913793103448</v>
       </c>
       <c r="H1" t="n">
-        <v>0.18882</v>
+        <v>0.1237096551724138</v>
       </c>
       <c r="I1" t="n">
-        <v>0.22029</v>
+        <v>0.1443279310344828</v>
       </c>
       <c r="J1" t="n">
-        <v>0.25176</v>
+        <v>0.1649462068965517</v>
       </c>
       <c r="K1" t="n">
-        <v>0.28323</v>
-      </c>
-      <c r="L1" t="n">
-        <v>0.3147</v>
-      </c>
-      <c r="M1" t="n">
-        <v>0.34617</v>
-      </c>
-      <c r="N1" t="n">
-        <v>0.37764</v>
-      </c>
-      <c r="O1" t="n">
-        <v>0.4091099999999999</v>
-      </c>
-      <c r="P1" t="n">
-        <v>0.44058</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>0.47205</v>
-      </c>
-      <c r="R1" t="n">
-        <v>0.50352</v>
-      </c>
-      <c r="S1" t="n">
-        <v>0.53499</v>
-      </c>
-      <c r="T1" t="n">
-        <v>0.56646</v>
-      </c>
-      <c r="U1" t="n">
-        <v>0.59793</v>
+        <v>0.1855644827586207</v>
       </c>
     </row>
     <row r="2">
@@ -483,64 +453,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00780487804878049</v>
+        <v>0.04490571233922953</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007904459644512002</v>
+        <v>0.04768578349733197</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00797896897069989</v>
+        <v>0.0499816503076356</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008030474760540045</v>
+        <v>0.05184076196987553</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008060909700888835</v>
+        <v>0.0533066547529927</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008072078515994494</v>
+        <v>0.05441924851730882</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008065665597878508</v>
+        <v>0.05521512186994251</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008043242207858382</v>
+        <v>0.05572776744243635</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008006273272414446</v>
+        <v>0.05598782867824895</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007956123795380767</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.007894064907281244</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.007821279571532459</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.007738867966192563</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.007647852558946986</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.007549182892084599</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.007443740093329338</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.007332341127549856</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.007215742803571116</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.007094645549554718</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.006969696969696968</v>
+        <v>0.05602331942322609</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +488,34 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00780487804878049</v>
+        <v>0.04490571233922953</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007904459644512002</v>
+        <v>0.04768578349733197</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00797896897069989</v>
+        <v>0.0499816503076356</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008030474760540045</v>
+        <v>0.05184076196987553</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008060909700888835</v>
+        <v>0.0533066547529927</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008072078515994494</v>
+        <v>0.05441924851730882</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008065665597878508</v>
+        <v>0.05521512186994251</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008043242207858382</v>
+        <v>0.05572776744243635</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008006273272414446</v>
+        <v>0.05598782867824895</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007956123795380767</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.007894064907281244</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.007821279571532459</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.007738867966192563</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.007647852558946986</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.007549182892084599</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.007443740093329338</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.007332341127549856</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.007215742803571116</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.007094645549554718</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.006969696969696968</v>
+        <v>0.05602331942322609</v>
       </c>
     </row>
   </sheetData>
